--- a/data/trans_orig/P36BPD11_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD11_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de veces que consumen repostería comercial a la semana en 2023</t>
+          <t>Población según el número de veces que consumen repostería comercial a la semana en 2023 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>137442</t>
+          <t>135620</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>179981</t>
+          <t>178742</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,79%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>107374</t>
+          <t>108992</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>137244</t>
+          <t>138077</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>255224</t>
+          <t>256219</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>306996</t>
+          <t>306016</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>50,91%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>91187</t>
+          <t>91668</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>132722</t>
+          <t>134510</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>108862</t>
+          <t>108439</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>137351</t>
+          <t>137781</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>47,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>209166</t>
+          <t>210844</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>260840</t>
+          <t>260690</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>43,37%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>29635</t>
+          <t>31364</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>64023</t>
+          <t>63999</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>33092</t>
+          <t>32446</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>58436</t>
+          <t>60590</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>67151</t>
+          <t>67750</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>109528</t>
+          <t>110271</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,35%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>187481</t>
+          <t>186131</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>247041</t>
+          <t>246399</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>47,66%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>209804</t>
+          <t>209619</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>249282</t>
+          <t>250341</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>48,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>409238</t>
+          <t>411299</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>482195</t>
+          <t>480409</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>46,49%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>217052</t>
+          <t>216652</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>276909</t>
+          <t>275828</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>53,21%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>204790</t>
+          <t>201960</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>244318</t>
+          <t>242711</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>47,44%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>435655</t>
+          <t>435032</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>508432</t>
+          <t>505438</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>42,1%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>48,91%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>42625</t>
+          <t>41968</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>81275</t>
+          <t>79054</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>49324</t>
+          <t>48470</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>75531</t>
+          <t>75816</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>98435</t>
+          <t>96946</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>144835</t>
+          <t>143838</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,92%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>138093</t>
+          <t>139474</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>174209</t>
+          <t>173773</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>55,12%</t>
+          <t>54,98%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>171124</t>
+          <t>169863</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>202577</t>
+          <t>202962</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>48,65%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>58,02%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>318394</t>
+          <t>318785</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>367157</t>
+          <t>366398</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>55,08%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>75087</t>
+          <t>74435</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>107854</t>
+          <t>107010</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>86638</t>
+          <t>86766</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>116563</t>
+          <t>116746</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>170758</t>
+          <t>170146</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>215174</t>
+          <t>213584</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,11%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>57274</t>
+          <t>55734</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>84344</t>
+          <t>85528</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>50323</t>
+          <t>50549</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>74568</t>
+          <t>74104</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>114367</t>
+          <t>113005</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>152353</t>
+          <t>151165</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,73%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>125202</t>
+          <t>126811</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>170402</t>
+          <t>172459</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>55,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>97404</t>
+          <t>100927</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>209591</t>
+          <t>205676</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>226989</t>
+          <t>228424</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>363067</t>
+          <t>364844</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>46,54%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>61228</t>
+          <t>60732</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>97967</t>
+          <t>98029</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>117054</t>
+          <t>111760</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>298256</t>
+          <t>285372</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>60,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>193606</t>
+          <t>190927</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>401545</t>
+          <t>404543</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>51,6%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>63656</t>
+          <t>64776</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>108725</t>
+          <t>110311</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>83971</t>
+          <t>84748</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>200750</t>
+          <t>210888</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>44,58%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>161706</t>
+          <t>160095</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>286210</t>
+          <t>286243</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>117112</t>
+          <t>118918</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>138656</t>
+          <t>139599</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>65,52%</t>
+          <t>66,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>78,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>154856</t>
+          <t>154654</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>172505</t>
+          <t>171646</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,52%</t>
+          <t>74,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>277593</t>
+          <t>278357</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>305288</t>
+          <t>305133</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>78,94%</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>23893</t>
+          <t>23916</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>43281</t>
+          <t>42609</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>19253</t>
+          <t>20003</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>33641</t>
+          <t>33402</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>47367</t>
+          <t>47853</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>70446</t>
+          <t>71454</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,48%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11681</t>
+          <t>11722</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>25703</t>
+          <t>24775</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13938</t>
+          <t>13844</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25100</t>
+          <t>26012</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>28661</t>
+          <t>27602</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>46530</t>
+          <t>45856</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,86%</t>
         </is>
       </c>
     </row>
@@ -3010,12 +3010,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>102330</t>
+          <t>103144</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>132093</t>
+          <t>133218</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>49,41%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>115448</t>
+          <t>115650</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>141707</t>
+          <t>143298</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>44,99%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>55,75%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>226845</t>
+          <t>228389</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>265763</t>
+          <t>266454</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>50,59%</t>
         </is>
       </c>
     </row>
@@ -3123,12 +3123,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>59936</t>
+          <t>59372</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>87202</t>
+          <t>86854</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3138,12 +3138,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>74393</t>
+          <t>73339</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>100266</t>
+          <t>98660</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3173,12 +3173,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>142512</t>
+          <t>141518</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>177139</t>
+          <t>178033</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,8%</t>
         </is>
       </c>
     </row>
@@ -3236,12 +3236,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>66055</t>
+          <t>64528</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>92854</t>
+          <t>93334</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3271,12 +3271,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>32817</t>
+          <t>32995</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>52092</t>
+          <t>51472</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>103519</t>
+          <t>104244</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>136202</t>
+          <t>137936</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>26,19%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>334393</t>
+          <t>332783</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>393883</t>
+          <t>391439</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>53,39%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>544639</t>
+          <t>543651</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>737573</t>
+          <t>737029</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>64,12%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>891111</t>
+          <t>892995</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1156811</t>
+          <t>1169062</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>60,7%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>79,47%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>114627</t>
+          <t>113516</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>164681</t>
+          <t>163656</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>56608</t>
+          <t>55241</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>165630</t>
+          <t>166791</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>170467</t>
+          <t>168365</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>315234</t>
+          <t>316579</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,52%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>99398</t>
+          <t>100058</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>147308</t>
+          <t>145492</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>48588</t>
+          <t>49718</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>144000</t>
+          <t>143950</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3742,7 +3742,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>135233</t>
+          <t>126972</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>275741</t>
+          <t>272847</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,55%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>232317</t>
+          <t>230474</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>698202</t>
+          <t>698941</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>75,26%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>204933</t>
+          <t>202808</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>246874</t>
+          <t>248737</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>463195</t>
+          <t>464397</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1019082</t>
+          <t>1026556</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>62,38%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>185892</t>
+          <t>183391</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>572304</t>
+          <t>570134</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>61,62%</t>
+          <t>61,39%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>399469</t>
+          <t>397091</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>444231</t>
+          <t>446233</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>55,38%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>61,96%</t>
+          <t>62,24%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>513369</t>
+          <t>524590</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>991103</t>
+          <t>990613</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>60,22%</t>
+          <t>60,19%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>41967</t>
+          <t>45177</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>132886</t>
+          <t>139375</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>56839</t>
+          <t>56416</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>84153</t>
+          <t>84643</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>101315</t>
+          <t>99742</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>199404</t>
+          <t>201525</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,25%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1551316</t>
+          <t>1560465</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2095125</t>
+          <t>2120679</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>45,14%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>61,34%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1705155</t>
+          <t>1699167</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2159875</t>
+          <t>2151185</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>58,83%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3325296</t>
+          <t>3324335</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4035101</t>
+          <t>4055399</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>46,73%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>56,72%</t>
+          <t>57,01%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>921631</t>
+          <t>936617</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1294714</t>
+          <t>1290988</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1077364</t>
+          <t>1065539</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1411226</t>
+          <t>1414550</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>2131153</t>
+          <t>2162248</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>2643408</t>
+          <t>2652470</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>37,29%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>441437</t>
+          <t>437713</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>636436</t>
+          <t>631582</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>443238</t>
+          <t>445627</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>617538</t>
+          <t>625199</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>962760</t>
+          <t>958600</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1223539</t>
+          <t>1203347</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>16,92%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36BPD11_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD11_2023-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>158000</t>
+          <t>166834</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>135620</t>
+          <t>148484</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>186832</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>52,32%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>58,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>123167</t>
+          <t>135950</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>108992</t>
+          <t>122961</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>138077</t>
+          <t>150537</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>281167</t>
+          <t>302784</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>256219</t>
+          <t>278068</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>306016</t>
+          <t>323872</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,91%</t>
+          <t>51,01%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>110570</t>
+          <t>107489</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>91668</t>
+          <t>89812</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>134510</t>
+          <t>126780</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>122888</t>
+          <t>133128</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>108439</t>
+          <t>118886</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>137781</t>
+          <t>147492</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>233458</t>
+          <t>240617</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>210844</t>
+          <t>219191</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>260690</t>
+          <t>264828</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>41,71%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>42872</t>
+          <t>44522</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31364</t>
+          <t>31696</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>63999</t>
+          <t>59147</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>43580</t>
+          <t>46983</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>32446</t>
+          <t>36431</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>60590</t>
+          <t>60168</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>86452</t>
+          <t>91505</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>67750</t>
+          <t>75258</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>110271</t>
+          <t>111995</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>17,64%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>213622</t>
+          <t>219465</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>186131</t>
+          <t>191623</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>246399</t>
+          <t>248822</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>229704</t>
+          <t>240494</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>209619</t>
+          <t>221371</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>250341</t>
+          <t>261157</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>443326</t>
+          <t>459958</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>411299</t>
+          <t>423064</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>480409</t>
+          <t>495969</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>46,04%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>246277</t>
+          <t>250956</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>216652</t>
+          <t>222250</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>275828</t>
+          <t>280083</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>52,78%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>224429</t>
+          <t>236878</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>201960</t>
+          <t>215416</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>242711</t>
+          <t>258082</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>39,42%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>470707</t>
+          <t>487834</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>435032</t>
+          <t>453132</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>505438</t>
+          <t>524444</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>48,69%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>58490</t>
+          <t>60226</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41968</t>
+          <t>43133</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>79054</t>
+          <t>79692</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>60836</t>
+          <t>69122</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>48470</t>
+          <t>56084</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>75816</t>
+          <t>84584</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>119326</t>
+          <t>129349</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>96946</t>
+          <t>108402</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>143838</t>
+          <t>157015</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,58%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>155595</t>
+          <t>155751</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>139474</t>
+          <t>139605</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>173773</t>
+          <t>172223</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>49,29%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>54,5%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>187147</t>
+          <t>192274</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>169863</t>
+          <t>176009</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>202962</t>
+          <t>208553</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>53,6%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>58,52%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>342742</t>
+          <t>348026</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>318785</t>
+          <t>325362</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>366398</t>
+          <t>372677</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>48,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>55,43%</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1750,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>90652</t>
+          <t>88173</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>74435</t>
+          <t>73526</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>107010</t>
+          <t>104300</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,32 +1785,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>100598</t>
+          <t>99933</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>86766</t>
+          <t>86627</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>116746</t>
+          <t>115129</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>191250</t>
+          <t>188107</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>170146</t>
+          <t>166984</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>213584</t>
+          <t>208709</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>31,04%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>69803</t>
+          <t>72069</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>55734</t>
+          <t>58341</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>85528</t>
+          <t>88975</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>61384</t>
+          <t>64173</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>50549</t>
+          <t>53298</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>74104</t>
+          <t>77337</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>131187</t>
+          <t>136242</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>113005</t>
+          <t>118294</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>151165</t>
+          <t>156308</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>23,25%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>149293</t>
+          <t>181326</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>126811</t>
+          <t>155650</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>172459</t>
+          <t>207387</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
+          <t>56,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>165099</t>
+          <t>188758</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>100927</t>
+          <t>168860</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>205676</t>
+          <t>208813</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>45,03%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>49,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>314392</t>
+          <t>370084</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>228424</t>
+          <t>340261</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>364844</t>
+          <t>402310</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>43,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>50,98%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>76861</t>
+          <t>87160</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>60732</t>
+          <t>68819</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>98029</t>
+          <t>108496</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>177307</t>
+          <t>118832</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>111760</t>
+          <t>102769</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>285372</t>
+          <t>138831</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>60,32%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>254168</t>
+          <t>205992</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>190927</t>
+          <t>180147</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>404543</t>
+          <t>233197</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>29,55%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>84780</t>
+          <t>101461</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>64776</t>
+          <t>78108</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>110311</t>
+          <t>129959</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>130655</t>
+          <t>111560</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>84748</t>
+          <t>94151</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>210888</t>
+          <t>129923</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>215436</t>
+          <t>213020</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>160095</t>
+          <t>182678</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>286243</t>
+          <t>245882</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>31,16%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>310934</t>
+          <t>369947</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>310934</t>
+          <t>369947</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>310934</t>
+          <t>369947</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>473061</t>
+          <t>419149</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>473061</t>
+          <t>419149</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>473061</t>
+          <t>419149</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>783995</t>
+          <t>789096</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>783995</t>
+          <t>789096</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>783995</t>
+          <t>789096</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>128902</t>
+          <t>150198</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>118918</t>
+          <t>137582</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>139599</t>
+          <t>160261</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>78,1%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,32 +2584,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>163491</t>
+          <t>177727</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>154654</t>
+          <t>167031</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>171646</t>
+          <t>186001</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>78,67%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>292393</t>
+          <t>327924</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>278357</t>
+          <t>311372</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>305133</t>
+          <t>341064</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>72,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>78,95%</t>
         </is>
       </c>
     </row>
@@ -2662,32 +2662,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>32325</t>
+          <t>36904</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>23916</t>
+          <t>28114</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>42609</t>
+          <t>48743</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,32 +2697,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>25764</t>
+          <t>29373</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>20003</t>
+          <t>22565</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>33402</t>
+          <t>38632</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>58089</t>
+          <t>66276</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>47853</t>
+          <t>55003</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>71454</t>
+          <t>80006</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,52%</t>
         </is>
       </c>
     </row>
@@ -2775,32 +2775,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>17515</t>
+          <t>18563</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11722</t>
+          <t>12654</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24775</t>
+          <t>26408</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,32 +2810,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>18560</t>
+          <t>19240</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13844</t>
+          <t>13795</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>26012</t>
+          <t>25838</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>36075</t>
+          <t>37802</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>27602</t>
+          <t>29428</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>45856</t>
+          <t>48234</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,17%</t>
         </is>
       </c>
     </row>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,17 +2923,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>207814</t>
+          <t>226339</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>207814</t>
+          <t>226339</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>207814</t>
+          <t>226339</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>386556</t>
+          <t>432003</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>386556</t>
+          <t>432003</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>386556</t>
+          <t>432003</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3005,32 +3005,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>117949</t>
+          <t>119223</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>103144</t>
+          <t>104401</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>133218</t>
+          <t>132760</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>49,04%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,67 +3040,67 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>129281</t>
+          <t>131418</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>115650</t>
+          <t>119115</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>143298</t>
+          <t>145137</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
+          <t>49,83%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>45,16%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>55,03%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>422</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>250641</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>231053</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>268782</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>46,9%</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>43,23%</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
           <t>50,29%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>44,99%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>55,75%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>422</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>247230</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>228389</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>266454</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>46,94%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>43,36%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>50,59%</t>
         </is>
       </c>
     </row>
@@ -3118,32 +3118,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>73135</t>
+          <t>73129</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>59372</t>
+          <t>59782</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>86854</t>
+          <t>87177</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,32 +3153,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>86075</t>
+          <t>88048</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>73339</t>
+          <t>76022</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>98660</t>
+          <t>101937</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>38,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,32 +3188,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>159210</t>
+          <t>161177</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>141518</t>
+          <t>144884</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>178033</t>
+          <t>181328</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,93%</t>
         </is>
       </c>
     </row>
@@ -3231,32 +3231,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>78552</t>
+          <t>78355</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>64528</t>
+          <t>65352</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>93334</t>
+          <t>92674</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,32 +3266,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>41701</t>
+          <t>44284</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>32995</t>
+          <t>35152</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>51472</t>
+          <t>53933</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,32 +3301,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>120253</t>
+          <t>122639</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>104244</t>
+          <t>106545</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>137936</t>
+          <t>139612</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,12%</t>
         </is>
       </c>
     </row>
@@ -3344,17 +3344,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3379,17 +3379,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3461,22 +3461,22 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>363102</t>
+          <t>416422</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>332783</t>
+          <t>383653</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>391439</t>
+          <t>444970</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>57,95%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>62,81%</t>
+          <t>61,92%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,32 +3496,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>624490</t>
+          <t>495434</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>543651</t>
+          <t>468798</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>737029</t>
+          <t>521170</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>64,29%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>64,12%</t>
+          <t>60,83%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>67,63%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,32 +3531,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>987592</t>
+          <t>911856</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>892995</t>
+          <t>871464</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1169062</t>
+          <t>951778</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>67,13%</t>
+          <t>61,23%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>60,7%</t>
+          <t>58,52%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>63,91%</t>
         </is>
       </c>
     </row>
@@ -3574,32 +3574,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>138807</t>
+          <t>157014</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>113516</t>
+          <t>132438</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>163656</t>
+          <t>185360</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,32 +3609,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>120378</t>
+          <t>147965</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>55241</t>
+          <t>125786</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>166791</t>
+          <t>169789</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,32 +3644,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>259185</t>
+          <t>304979</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>168365</t>
+          <t>272472</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>316579</t>
+          <t>341515</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>22,93%</t>
         </is>
       </c>
     </row>
@@ -3687,32 +3687,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>121341</t>
+          <t>145170</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>100058</t>
+          <t>121599</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>145492</t>
+          <t>171643</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,32 +3722,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>103035</t>
+          <t>127229</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>49718</t>
+          <t>107996</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>143950</t>
+          <t>147998</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,32 +3757,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>224376</t>
+          <t>272398</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>126972</t>
+          <t>244032</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>272847</t>
+          <t>304553</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>20,45%</t>
         </is>
       </c>
     </row>
@@ -3800,17 +3800,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>623250</t>
+          <t>718605</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>623250</t>
+          <t>718605</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>623250</t>
+          <t>718605</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3835,17 +3835,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>847903</t>
+          <t>770628</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>847903</t>
+          <t>770628</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>847903</t>
+          <t>770628</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3870,17 +3870,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1471153</t>
+          <t>1489233</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1471153</t>
+          <t>1489233</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1471153</t>
+          <t>1489233</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3917,32 +3917,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>421554</t>
+          <t>211990</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>230474</t>
+          <t>187115</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>698941</t>
+          <t>239941</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>75,26%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3952,32 +3952,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>225692</t>
+          <t>257462</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>202808</t>
+          <t>232602</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>248737</t>
+          <t>280043</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,32 +3987,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>647246</t>
+          <t>469451</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>464397</t>
+          <t>436703</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1026556</t>
+          <t>509632</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>31,29%</t>
         </is>
       </c>
     </row>
@@ -4030,32 +4030,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>413894</t>
+          <t>480486</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>183391</t>
+          <t>452782</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>570134</t>
+          <t>508789</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>60,21%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>56,73%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4065,32 +4065,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>422120</t>
+          <t>488830</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>397091</t>
+          <t>462013</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>446233</t>
+          <t>514802</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>58,87%</t>
+          <t>58,86%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>55,63%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>61,98%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4100,32 +4100,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>836014</t>
+          <t>969316</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>524590</t>
+          <t>925821</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>990613</t>
+          <t>1007384</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>56,85%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>60,19%</t>
+          <t>61,86%</t>
         </is>
       </c>
     </row>
@@ -4143,32 +4143,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>93272</t>
+          <t>105596</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>45177</t>
+          <t>85671</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>139375</t>
+          <t>126348</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4178,32 +4178,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>69191</t>
+          <t>84246</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>56416</t>
+          <t>68066</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>84643</t>
+          <t>104149</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4213,32 +4213,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>162463</t>
+          <t>189842</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>99742</t>
+          <t>165259</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>201525</t>
+          <t>219384</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>13,47%</t>
         </is>
       </c>
     </row>
@@ -4256,17 +4256,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4291,17 +4291,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>717003</t>
+          <t>830537</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>717003</t>
+          <t>830537</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>717003</t>
+          <t>830537</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4326,17 +4326,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>1645723</t>
+          <t>1628609</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1645723</t>
+          <t>1628609</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>1645723</t>
+          <t>1628609</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4373,32 +4373,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>1708017</t>
+          <t>1621208</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1560465</t>
+          <t>1552429</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2120679</t>
+          <t>1683890</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>45,95%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>44,0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>47,72%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4408,32 +4408,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>1848070</t>
+          <t>1819517</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1699167</t>
+          <t>1760876</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2151185</t>
+          <t>1869046</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>48,79%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>47,22%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>58,83%</t>
+          <t>50,12%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4443,32 +4443,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>3556088</t>
+          <t>3440725</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3324335</t>
+          <t>3358972</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4055399</t>
+          <t>3518196</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>46,28%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>57,01%</t>
+          <t>48,47%</t>
         </is>
       </c>
     </row>
@@ -4486,32 +4486,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>1182522</t>
+          <t>1281311</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>936617</t>
+          <t>1217939</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1290988</t>
+          <t>1344833</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4521,32 +4521,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>1279558</t>
+          <t>1342987</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1065539</t>
+          <t>1289892</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1414550</t>
+          <t>1398694</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4556,32 +4556,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>2462079</t>
+          <t>2624298</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>2162248</t>
+          <t>2548013</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>2652470</t>
+          <t>2716157</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>37,42%</t>
         </is>
       </c>
     </row>
@@ -4599,32 +4599,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>566626</t>
+          <t>625963</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>437713</t>
+          <t>574518</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>631582</t>
+          <t>681426</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4634,32 +4634,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>528940</t>
+          <t>566836</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>445627</t>
+          <t>525036</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>625199</t>
+          <t>606701</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4669,32 +4669,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1095566</t>
+          <t>1192799</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>958600</t>
+          <t>1126219</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1203347</t>
+          <t>1259873</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,36%</t>
         </is>
       </c>
     </row>
@@ -4712,17 +4712,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>3457165</t>
+          <t>3528482</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>3457165</t>
+          <t>3528482</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>3457165</t>
+          <t>3528482</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4747,17 +4747,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>3656568</t>
+          <t>3729340</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>3656568</t>
+          <t>3729340</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>3656568</t>
+          <t>3729340</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>7113733</t>
+          <t>7257822</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>7113733</t>
+          <t>7257822</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>7113733</t>
+          <t>7257822</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
